--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/PARAFUSO RABETA.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/PARAFUSO RABETA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,11 +432,6 @@
           <t>QUANTIDADE</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>PREÇO</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -457,11 +452,6 @@
           <t>60</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -478,7 +468,6 @@
           <t> </t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
